--- a/data.mn/public/datasets/mongolbank-credit-private-sector.xlsx
+++ b/data.mn/public/datasets/mongolbank-credit-private-sector.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
   <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -520,10 +520,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Month 1</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>249.88</v>
@@ -596,10 +594,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Month 2</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="n">
         <v>262.93</v>
@@ -667,13 +663,13 @@
       <c r="W3" t="n">
         <v>13877.83</v>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>16959.67</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Month 3</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="n">
         <v>279.13</v>
@@ -741,13 +737,13 @@
       <c r="W4" t="n">
         <v>14381.05</v>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>17335.9</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Month 4</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>304.28</v>
@@ -815,13 +811,13 @@
       <c r="W5" t="n">
         <v>14800.9</v>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>17909.96</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Month 5</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="n">
         <v>310.22</v>
@@ -889,13 +885,13 @@
       <c r="W6" t="n">
         <v>15258.12</v>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>18653.5</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Month 6</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="n">
         <v>315.22</v>
@@ -963,13 +959,13 @@
       <c r="W7" t="n">
         <v>16550.62</v>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>19540.43</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Month 7</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="n">
         <v>324.81</v>
@@ -1037,13 +1033,13 @@
       <c r="W8" t="n">
         <v>16295.3</v>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>19103.76</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Month 8</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="n">
         <v>334.44</v>
@@ -1111,13 +1107,10 @@
       <c r="W9" t="n">
         <v>16427.12</v>
       </c>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Month 9</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="n">
         <v>334.52</v>
@@ -1185,13 +1178,10 @@
       <c r="W10" t="n">
         <v>16570.1</v>
       </c>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Month 10</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="n">
         <v>344.26</v>
@@ -1259,13 +1249,10 @@
       <c r="W11" t="n">
         <v>16942.64</v>
       </c>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Month 11</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="n">
         <v>357.95</v>
@@ -1333,13 +1320,10 @@
       <c r="W12" t="n">
         <v>16918.92</v>
       </c>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Month 12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="n">
         <v>365.06</v>
@@ -1407,7 +1391,6 @@
       <c r="W13" t="n">
         <v>17196.36</v>
       </c>
-      <c r="X13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1423,7 +1406,7 @@
   <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -1526,10 +1509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1-р сар</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>249.88</v>
@@ -1602,10 +1583,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2-р сар</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="n">
         <v>262.93</v>
@@ -1673,13 +1652,13 @@
       <c r="W3" t="n">
         <v>13877.83</v>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>16959.67</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3-р сар</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="n">
         <v>279.13</v>
@@ -1747,13 +1726,13 @@
       <c r="W4" t="n">
         <v>14381.05</v>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>17335.9</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4-р сар</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>304.28</v>
@@ -1821,13 +1800,13 @@
       <c r="W5" t="n">
         <v>14800.9</v>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>17909.96</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5-р сар</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="n">
         <v>310.22</v>
@@ -1895,13 +1874,13 @@
       <c r="W6" t="n">
         <v>15258.12</v>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>18653.5</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6-р сар</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="n">
         <v>315.22</v>
@@ -1969,13 +1948,13 @@
       <c r="W7" t="n">
         <v>16550.62</v>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>19540.43</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7-р сар</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="n">
         <v>324.81</v>
@@ -2043,13 +2022,13 @@
       <c r="W8" t="n">
         <v>16295.3</v>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>19103.76</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8-р сар</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="n">
         <v>334.44</v>
@@ -2117,13 +2096,10 @@
       <c r="W9" t="n">
         <v>16427.12</v>
       </c>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9-р сар</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="n">
         <v>334.52</v>
@@ -2191,13 +2167,10 @@
       <c r="W10" t="n">
         <v>16570.1</v>
       </c>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10-р сар</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="n">
         <v>344.26</v>
@@ -2265,13 +2238,10 @@
       <c r="W11" t="n">
         <v>16942.64</v>
       </c>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11-р сар</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="n">
         <v>357.95</v>
@@ -2339,13 +2309,10 @@
       <c r="W12" t="n">
         <v>16918.92</v>
       </c>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12-р сар</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="n">
         <v>365.06</v>
@@ -2413,7 +2380,6 @@
       <c r="W13" t="n">
         <v>17196.36</v>
       </c>
-      <c r="X13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
